--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -28,6 +28,9 @@
     <t xml:space="preserve">Sample bypass pumps</t>
   </si>
   <si>
+    <t xml:space="preserve">K-Type Thermocouple sensors</t>
+  </si>
+  <si>
     <t xml:space="preserve">Address</t>
   </si>
   <si>
@@ -37,12 +40,18 @@
     <t xml:space="preserve">VNH5019 motor driver_ Dual peristatic pumps</t>
   </si>
   <si>
+    <t xml:space="preserve">6 SPI Thermal sensor interface to ESP32-nodemcu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Board</t>
   </si>
   <si>
     <t xml:space="preserve">Arduino UNO</t>
   </si>
   <si>
+    <t xml:space="preserve">ESP-nodemcu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coil_0</t>
   </si>
   <si>
@@ -52,43 +61,178 @@
     <t xml:space="preserve">Coil_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Discrete_input_0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coil_2</t>
   </si>
   <si>
+    <t xml:space="preserve">Holding_register_0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coil_3</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set M1 speed (0 to 400)</t>
+    <t xml:space="preserve">Input_register_0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sample temperature  </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sample stabilised temp </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Discrete_input_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">water temperature  </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Discrete_input_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">water stabilised temp </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">set M1 speed, range:-400:400</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_1</t>
   </si>
   <si>
-    <t xml:space="preserve">set M2 speed (0 to 400)</t>
+    <t xml:space="preserve">set M2 speed, range:-400:400</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_2</t>
   </si>
   <si>
-    <t xml:space="preserve">set M1 brake (0 to 400)</t>
+    <t xml:space="preserve">set M1 brake, range:0:400</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_3</t>
   </si>
   <si>
-    <t xml:space="preserve">set M2 brake (0 to 400)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_0</t>
+    <t xml:space="preserve">set M2 brake, range:0:400</t>
   </si>
   <si>
     <t xml:space="preserve">M1 current (mA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_1</t>
   </si>
   <si>
     <t xml:space="preserve">M2 current (mA)</t>
@@ -101,7 +245,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -123,6 +267,13 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -132,7 +283,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -140,6 +291,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -166,12 +359,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -192,131 +409,227 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="39.16"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="4" style="1" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.58"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="1" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="0"/>
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="0"/>
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="0"/>
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="0"/>
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="0"/>
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="0"/>
+      <c r="D14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="B16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="B17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -31,6 +31,9 @@
     <t xml:space="preserve">K-Type Thermocouple sensors</t>
   </si>
   <si>
+    <t xml:space="preserve">Sample extraction module</t>
+  </si>
+  <si>
     <t xml:space="preserve">Address</t>
   </si>
   <si>
@@ -43,6 +46,9 @@
     <t xml:space="preserve">6 SPI Thermal sensor interface to ESP32-nodemcu</t>
   </si>
   <si>
+    <t xml:space="preserve">2 x Peristatic pump, load cell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Board</t>
   </si>
   <si>
@@ -55,175 +61,70 @@
     <t xml:space="preserve">Coil_0</t>
   </si>
   <si>
+    <t xml:space="preserve">Enable M1 brake</t>
+  </si>
+  <si>
     <t xml:space="preserve">NA</t>
   </si>
   <si>
     <t xml:space="preserve">Coil_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Enable M2 brake</t>
+  </si>
+  <si>
     <t xml:space="preserve">Discrete_input_0</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_2</t>
+    <t xml:space="preserve">Fault for M1 ?</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_0</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_3</t>
+    <t xml:space="preserve">Discrete_input_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fault for M2 ?</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_0</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sample temperature  </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
+    <t xml:space="preserve">sample temperature  C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set M1 speed, range:-400:400</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_1</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sample stabilised temp </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Discrete_input_1</t>
+    <t xml:space="preserve">sample stabilised temp C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set M2 speed, range:-400:400</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">water temperature  </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Discrete_input_2</t>
+    <t xml:space="preserve">water temperature C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set M1 brake, range:0:400</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">water stabilised temp </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">set M1 speed, range:-400:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set M2 speed, range:-400:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set M1 brake, range:0:400</t>
+    <t xml:space="preserve">water stabilised temp C</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_3</t>
@@ -245,7 +146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -267,23 +168,22 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEE6EF"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -293,43 +193,8 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -359,7 +224,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -368,28 +233,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -401,6 +262,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFDEE6EF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -409,21 +330,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.58"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="1" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="35.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="11.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -432,204 +355,249 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="n">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="F2" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>8</v>
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>11</v>
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>11</v>
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>11</v>
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>11</v>
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>11</v>
+      <c r="A11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>27</v>
+      <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="C12" s="0"/>
       <c r="D12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>29</v>
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C13" s="0"/>
       <c r="D13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>31</v>
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C14" s="0"/>
       <c r="D14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="0"/>
       <c r="D16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="0"/>
       <c r="D17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0"/>
+      <c r="B20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0"/>
+      <c r="B22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0"/>
+      <c r="B23" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -8,7 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="MAIN" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="DUMP" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,123 +21,186 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample bypass pumps</t>
+    <t xml:space="preserve">Sample and water pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature equalisation module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample extraction module rs485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VNH5019 motor driver: 2 x peristatic pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 SPI Thermal sensor interface, 4 valves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x Peristatic pump, load cell, DHT22 over RS485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arduino UNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mega 2560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable Module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable module/ Emergency Power OFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable M1 brake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discrete_input_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable Humidity &amp; Temperature sensor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable M2 brake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable load cell sensor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fault for M1 ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sample temperature  C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable pump 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discrete_input_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fault for M2 ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sample stabilised temp C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable pump 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M1 speed, range:-400:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water temperature C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humidity &amp; Temperature sensor error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M2 speed, range:-400:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water stabilised temp C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M1 brake, range:0:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set pump 1 flow rate, range:0:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M2 brake, range:0:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 current (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 current (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humidity (RH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature (deg C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight (grams)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor 1 current sense (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor 2 current sense (mA)</t>
   </si>
   <si>
     <t xml:space="preserve">K-Type Thermocouple sensors</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample extraction module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VNH5019 motor driver_ Dual peristatic pumps</t>
-  </si>
-  <si>
     <t xml:space="preserve">6 SPI Thermal sensor interface to ESP32-nodemcu</t>
   </si>
   <si>
-    <t xml:space="preserve">2 x Peristatic pump, load cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Board</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arduino UNO</t>
-  </si>
-  <si>
     <t xml:space="preserve">ESP-nodemcu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coil_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable M1 brake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coil_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable M2 brake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discrete_input_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fault for M1 ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discrete_input_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fault for M2 ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sample temperature  C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set M1 speed, range:-400:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sample stabilised temp C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set M2 speed, range:-400:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water temperature C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set M1 brake, range:0:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water stabilised temp C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set M2 brake, range:0:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 current (mA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2 current (mA)</t>
   </si>
 </sst>
 </file>
@@ -146,7 +210,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -168,8 +232,13 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -179,7 +248,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDEE6EF"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFF6F9D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFA6"/>
+        <bgColor rgb="FFF6F9D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9D4"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -224,7 +305,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -237,15 +318,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -282,7 +387,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFF6F9D4"/>
       <rgbColor rgb="FFDEE6EF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -299,7 +404,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFFFA6"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -330,35 +435,35 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="35.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.91"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="11.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -366,39 +471,39 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>3</v>
+      <c r="F2" s="5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -406,198 +511,315 @@
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="5" t="s">
         <v>9</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0"/>
+        <v>43</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0"/>
+        <v>46</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="0"/>
-      <c r="D14" s="0"/>
+      <c r="B14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="0"/>
       <c r="D16" s="0"/>
+      <c r="E16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
       <c r="C17" s="0"/>
       <c r="D17" s="0"/>
+      <c r="E17" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0"/>
-      <c r="B18" s="0"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="E18" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0"/>
       <c r="B19" s="0"/>
+      <c r="E19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0"/>
       <c r="B20" s="0"/>
+      <c r="E20" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0"/>
       <c r="B21" s="0"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0"/>
       <c r="B22" s="0"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0"/>
-      <c r="B23" s="6"/>
+      <c r="B23" s="0"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0"/>
+      <c r="B24" s="12"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -608,4 +830,111 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="68.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="62">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Discrete_input_0</t>
   </si>
   <si>
-    <t xml:space="preserve">Enable Humidity &amp; Temperature sensor</t>
+    <t xml:space="preserve">Get humidity &amp; Temperature</t>
   </si>
   <si>
     <t xml:space="preserve">Coil_2</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Holding_register_0</t>
   </si>
   <si>
-    <t xml:space="preserve">Enable load cell sensor</t>
+    <t xml:space="preserve">Get sample weight (avg of 5)</t>
   </si>
   <si>
     <t xml:space="preserve">Fault for M1 ?</t>
@@ -137,40 +137,46 @@
     <t xml:space="preserve">water temperature C</t>
   </si>
   <si>
+    <t xml:space="preserve">Coil_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tare load cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M2 speed, range:-400:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water stabilised temp C</t>
+  </si>
+  <si>
     <t xml:space="preserve">Humidity &amp; Temperature sensor error</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set M2 speed, range:-400:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water stabilised temp C</t>
-  </si>
-  <si>
     <t xml:space="preserve">Holding_register_2</t>
   </si>
   <si>
     <t xml:space="preserve">Set M1 brake, range:0:400</t>
   </si>
   <si>
+    <t xml:space="preserve">Holding_register_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M2 brake, range:0:400</t>
+  </si>
+  <si>
     <t xml:space="preserve">Set pump 1 flow rate, range:0:100</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set M2 brake, range:0:400</t>
+    <t xml:space="preserve">M1 current (mA)</t>
   </si>
   <si>
     <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 current (mA)</t>
   </si>
   <si>
     <t xml:space="preserve">M2 current (mA)</t>
@@ -210,7 +216,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -231,11 +237,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -305,7 +306,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -343,14 +344,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -435,14 +428,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.91"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="11.52"/>
   </cols>
@@ -547,7 +540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -640,63 +633,63 @@
       <c r="D10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>18</v>
+      <c r="E10" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -704,15 +697,15 @@
         <v>25</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -720,15 +713,15 @@
         <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -736,11 +729,11 @@
       <c r="B16" s="9"/>
       <c r="C16" s="0"/>
       <c r="D16" s="0"/>
-      <c r="E16" s="5" t="s">
-        <v>25</v>
+      <c r="E16" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -748,42 +741,38 @@
       <c r="B17" s="9"/>
       <c r="C17" s="0"/>
       <c r="D17" s="0"/>
-      <c r="E17" s="10" t="s">
-        <v>31</v>
+      <c r="E17" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="E18" s="11" t="s">
-        <v>36</v>
+      <c r="E18" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0"/>
       <c r="B19" s="0"/>
-      <c r="E19" s="11" t="s">
-        <v>41</v>
+      <c r="E19" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0"/>
       <c r="B20" s="0"/>
-      <c r="E20" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0"/>
@@ -805,7 +794,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0"/>
-      <c r="B24" s="12"/>
+      <c r="B24" s="10"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
@@ -816,10 +805,6 @@
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -838,14 +823,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -861,7 +846,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -869,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -922,10 +907,10 @@
     </row>
     <row r="11" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Holding_register_0</t>
   </si>
   <si>
-    <t xml:space="preserve">Get sample weight (avg of 5)</t>
+    <t xml:space="preserve">Get sample weight (1 value, not avg) </t>
   </si>
   <si>
     <t xml:space="preserve">Fault for M1 ?</t>
@@ -823,7 +823,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="65">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -140,9 +140,6 @@
     <t xml:space="preserve">Coil_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Tare load cell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Holding_register_1</t>
   </si>
   <si>
@@ -155,33 +152,39 @@
     <t xml:space="preserve">water stabilised temp C</t>
   </si>
   <si>
+    <t xml:space="preserve">Coil_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset Slave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M1 brake, range:0:400</t>
+  </si>
+  <si>
     <t xml:space="preserve">Humidity &amp; Temperature sensor error</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set M1 brake, range:0:400</t>
-  </si>
-  <si>
     <t xml:space="preserve">Holding_register_3</t>
   </si>
   <si>
     <t xml:space="preserve">Set M2 brake, range:0:400</t>
   </si>
   <si>
+    <t xml:space="preserve">M1 current (mA)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Set pump 1 flow rate, range:0:100</t>
   </si>
   <si>
-    <t xml:space="preserve">M1 current (mA)</t>
+    <t xml:space="preserve">M2 current (mA)</t>
   </si>
   <si>
     <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
   </si>
   <si>
-    <t xml:space="preserve">M2 current (mA)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Humidity (RH)</t>
   </si>
   <si>
@@ -191,10 +194,16 @@
     <t xml:space="preserve">Weight (grams)</t>
   </si>
   <si>
+    <t xml:space="preserve">Un-tared weight(grams)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Motor 1 current sense (mA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Input_register_4</t>
+    <t xml:space="preserve">Input_register_5</t>
   </si>
   <si>
     <t xml:space="preserve">Motor 2 current sense (mA)</t>
@@ -428,7 +437,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.95"/>
@@ -637,24 +646,24 @@
         <v>38</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>44</v>
@@ -670,26 +679,26 @@
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -702,7 +711,7 @@
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="5" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>51</v>
@@ -718,7 +727,7 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>53</v>
@@ -729,8 +738,8 @@
       <c r="B16" s="9"/>
       <c r="C16" s="0"/>
       <c r="D16" s="0"/>
-      <c r="E16" s="4" t="s">
-        <v>31</v>
+      <c r="E16" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>54</v>
@@ -741,8 +750,8 @@
       <c r="B17" s="9"/>
       <c r="C17" s="0"/>
       <c r="D17" s="0"/>
-      <c r="E17" s="5" t="s">
-        <v>36</v>
+      <c r="E17" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>55</v>
@@ -752,7 +761,7 @@
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="E18" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>56</v>
@@ -762,23 +771,31 @@
       <c r="A19" s="0"/>
       <c r="B19" s="0"/>
       <c r="E19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0"/>
       <c r="B20" s="0"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0"/>
       <c r="B21" s="0"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0"/>
@@ -805,6 +822,14 @@
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -823,14 +848,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -846,7 +871,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -854,7 +879,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -907,10 +932,10 @@
     </row>
     <row r="11" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="109">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -65,157 +65,289 @@
     <t xml:space="preserve">Enable Module</t>
   </si>
   <si>
+    <t xml:space="preserve">Enable module/ Emergency Power OFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable module/ Emergency Power OFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable M1 brake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water relay ON/OFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get humidity &amp; Temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable M2 brake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get valve positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get sample weight (1 value, not avg) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discrete_input_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fault for M1 ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable pump 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discrete_input_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fault for M2 ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get temperatures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable pump 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M1 speed, range:-400:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset Slave</t>
+  </si>
+  <si>
     <t xml:space="preserve">NA</t>
   </si>
   <si>
-    <t xml:space="preserve">Enable module/ Emergency Power OFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coil_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable M1 brake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discrete_input_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get humidity &amp; Temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coil_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable M2 brake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get sample weight (1 value, not avg) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fault for M1 ?</t>
+    <t xml:space="preserve">Holding_register_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M2 speed, range:-400:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coil_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M1 brake, range:0:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humidity &amp; Temperature sensor error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set M2 brake, range:0:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve 1 (A) position, range:1:2</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_0</t>
   </si>
   <si>
+    <t xml:space="preserve">M1 current (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve 2 (B) position, range:1:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set pump 1 flow rate, range:0:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 current (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve 3 (A) position, range:1:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve 4 (B) position, range:1:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humidity (RH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve 5 position, range:1:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature (deg C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve 6 position, range:1:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight (grams)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set water cut off temperature, range:20:50:0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un-tared weight(grams)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set sample cut off temperature, range:20:50:0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor 1 current sense (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set water pump, range:0:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor 2 current sense (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set sample pump, range:0:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding_register_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valve 1 position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valve 2 position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valve 3 position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valve 4 position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valve 5 position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valve 6 position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature 1 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature 2 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature 3 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature 4 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature 5 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input_register_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature 6 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-Type Thermocouple sensors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 SPI Thermal sensor interface to ESP32-nodemcu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP-nodemcu</t>
+  </si>
+  <si>
     <t xml:space="preserve">sample temperature  C</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable pump 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discrete_input_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fault for M2 ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_1</t>
-  </si>
-  <si>
     <t xml:space="preserve">sample stabilised temp C</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable pump 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set M1 speed, range:-400:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">water temperature C</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set M2 speed, range:-400:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">water stabilised temp C</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset Slave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set M1 brake, range:0:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humidity &amp; Temperature sensor error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set M2 brake, range:0:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 current (mA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set pump 1 flow rate, range:0:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2 current (mA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humidity (RH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature (deg C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight (grams)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Un-tared weight(grams)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor 1 current sense (mA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input_register_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor 2 current sense (mA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K-Type Thermocouple sensors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 SPI Thermal sensor interface to ESP32-nodemcu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESP-nodemcu</t>
+    <t xml:space="preserve">Coil_7</t>
   </si>
 </sst>
 </file>
@@ -315,7 +447,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -344,10 +476,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -357,6 +485,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,13 +573,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="41.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.91"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="11.52"/>
@@ -480,7 +616,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>4</v>
@@ -529,7 +665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -557,10 +693,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>16</v>
@@ -577,10 +713,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>20</v>
@@ -591,19 +727,19 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>28</v>
@@ -623,15 +759,15 @@
         <v>32</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>35</v>
@@ -643,10 +779,10 @@
         <v>37</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -657,61 +793,73 @@
         <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E12" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+        <v>46</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="E13" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
       <c r="E14" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>51</v>
@@ -719,117 +867,283 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="E15" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="0"/>
-      <c r="D16" s="0"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="E16" s="5" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="0"/>
-      <c r="D17" s="0"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="E17" s="4" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="E18" s="5" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0"/>
       <c r="B19" s="0"/>
+      <c r="C19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="E19" s="5" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0"/>
       <c r="B20" s="0"/>
+      <c r="C20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E20" s="5" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0"/>
       <c r="B21" s="0"/>
+      <c r="C21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="E21" s="5" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0"/>
       <c r="B22" s="0"/>
+      <c r="C22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0"/>
       <c r="B23" s="0"/>
+      <c r="C23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0"/>
-      <c r="B24" s="10"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="0"/>
+      <c r="D40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C41" s="0"/>
+      <c r="D41" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -847,15 +1161,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -871,7 +1185,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -879,7 +1193,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -887,55 +1201,103 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>42</v>
+      <c r="B18" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="103">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">Holding_register_0</t>
   </si>
   <si>
-    <t xml:space="preserve">Set M1 speed, range:-400:400</t>
+    <t xml:space="preserve">Set M1 speed, range:-100:100</t>
   </si>
   <si>
     <t xml:space="preserve">Coil_5</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">Holding_register_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Set M2 speed, range:-400:400</t>
+    <t xml:space="preserve">Set M2 speed, range:-100:100</t>
   </si>
   <si>
     <t xml:space="preserve">Coil_6</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">Holding_register_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Set M1 brake, range:0:400</t>
+    <t xml:space="preserve">Set M1 brake, range:0:100</t>
   </si>
   <si>
     <t xml:space="preserve">Humidity &amp; Temperature sensor error</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">Holding_register_3</t>
   </si>
   <si>
-    <t xml:space="preserve">Set M2 brake, range:0:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set valve 1 (A) position, range:1:2</t>
+    <t xml:space="preserve">Set M2 brake, range:0:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve 1 (A) position, pulse:950:1900</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_0</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">M1 current (mA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 2 (B) position, range:1:2</t>
+    <t xml:space="preserve">Set valve 2 (B) position, pulse:950:1900</t>
   </si>
   <si>
     <t xml:space="preserve">Set pump 1 flow rate, range:0:100</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">M2 current (mA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 3 (A) position, range:1:2</t>
+    <t xml:space="preserve">Set valve 3 (A) position, pulse:1100:2000</t>
   </si>
   <si>
     <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">Holding_register_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 4 (B) position, range:1:2</t>
+    <t xml:space="preserve">Set valve 4 (B) position, pulse:1000:1900</t>
   </si>
   <si>
     <t xml:space="preserve">Humidity (RH)</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">Holding_register_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 5 position, range:1:2</t>
+    <t xml:space="preserve">Set valve 5 position, pulse:900:1900</t>
   </si>
   <si>
     <t xml:space="preserve">Temperature (deg C)</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Holding_register_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 6 position, range:1:2</t>
+    <t xml:space="preserve">Set valve 6 position, pulse:990:1900</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_2</t>
@@ -269,25 +269,7 @@
     <t xml:space="preserve">Holding_register_12</t>
   </si>
   <si>
-    <t xml:space="preserve">Valve 1 position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valve 2 position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valve 3 position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valve 4 position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valve 5 position</t>
-  </si>
-  <si>
     <t xml:space="preserve">Input_register_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valve 6 position</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_7</t>
@@ -573,13 +555,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:AMJ41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="41.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="41.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.91"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="11.52"/>
@@ -916,6 +898,8 @@
       <c r="F17" s="5" t="s">
         <v>61</v>
       </c>
+      <c r="AMI17" s="0"/>
+      <c r="AMJ17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
@@ -1032,7 +1016,7 @@
         <v>52</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1042,7 +1026,7 @@
         <v>64</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1052,7 +1036,7 @@
         <v>68</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -1062,7 +1046,7 @@
         <v>72</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1070,63 +1054,63 @@
         <v>76</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1162,14 +1146,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1185,7 +1169,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1193,7 +1177,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1225,7 +1209,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1233,7 +1217,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1241,7 +1225,7 @@
         <v>64</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1249,7 +1233,7 @@
         <v>68</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1294,7 +1278,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -1146,7 +1146,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="102">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -203,16 +203,13 @@
     <t xml:space="preserve">Holding_register_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 5 position, pulse:900:1900</t>
+    <t xml:space="preserve">Set valve 5 position(sample or water) pulse:1000:1950</t>
   </si>
   <si>
     <t xml:space="preserve">Temperature (deg C)</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set valve 6 position, pulse:990:1900</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_2</t>
@@ -883,7 +880,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="8"/>
       <c r="C17" s="3" t="s">
@@ -908,71 +905,71 @@
         <v>62</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0"/>
       <c r="B19" s="0"/>
       <c r="C19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0"/>
       <c r="B20" s="0"/>
       <c r="C20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0"/>
       <c r="B21" s="0"/>
       <c r="C21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0"/>
       <c r="B22" s="0"/>
       <c r="C22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -981,7 +978,7 @@
       <c r="A23" s="0"/>
       <c r="B23" s="0"/>
       <c r="C23" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>38</v>
@@ -993,7 +990,7 @@
       <c r="A24" s="0"/>
       <c r="B24" s="9"/>
       <c r="C24" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>38</v>
@@ -1023,7 +1020,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>38</v>
@@ -1033,7 +1030,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>38</v>
@@ -1043,7 +1040,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>38</v>
@@ -1051,7 +1048,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>38</v>
@@ -1059,7 +1056,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>38</v>
@@ -1067,50 +1064,50 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1146,14 +1143,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1169,7 +1166,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1177,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1209,7 +1206,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1217,23 +1214,23 @@
         <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1278,7 +1275,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="102">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -95,19 +95,31 @@
     <t xml:space="preserve">Get sample weight (1 value, not avg) </t>
   </si>
   <si>
+    <t xml:space="preserve">Coil_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset Slave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set valve positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable pump 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Discrete_input_0</t>
   </si>
   <si>
     <t xml:space="preserve">Fault for M1 ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set valve positions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable pump 1</t>
+    <t xml:space="preserve">Coil_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get temperatures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable pump 2</t>
   </si>
   <si>
     <t xml:space="preserve">Discrete_input_1</t>
@@ -116,13 +128,10 @@
     <t xml:space="preserve">Fault for M2 ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get temperatures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable pump 2</t>
+    <t xml:space="preserve">Coil_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_0</t>
@@ -131,13 +140,7 @@
     <t xml:space="preserve">Set M1 speed, range:-100:100</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset Slave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
+    <t xml:space="preserve">Coil_6</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_1</t>
@@ -146,7 +149,7 @@
     <t xml:space="preserve">Set M2 speed, range:-100:100</t>
   </si>
   <si>
-    <t xml:space="preserve">Coil_6</t>
+    <t xml:space="preserve">Humidity &amp; Temperature sensor error</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_2</t>
@@ -155,7 +158,7 @@
     <t xml:space="preserve">Set M1 brake, range:0:100</t>
   </si>
   <si>
-    <t xml:space="preserve">Humidity &amp; Temperature sensor error</t>
+    <t xml:space="preserve">Set valve 1 (A) position, pulse:950:1900</t>
   </si>
   <si>
     <t xml:space="preserve">Holding_register_3</t>
@@ -164,7 +167,10 @@
     <t xml:space="preserve">Set M2 brake, range:0:100</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 1 (A) position, pulse:950:1900</t>
+    <t xml:space="preserve">Set valve 2 (B) position, pulse:950:1900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set pump 1 flow rate, range:0:100</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_0</t>
@@ -173,10 +179,10 @@
     <t xml:space="preserve">M1 current (mA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 2 (B) position, pulse:950:1900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set pump 1 flow rate, range:0:100</t>
+    <t xml:space="preserve">Set valve 3 (A) position, pulse:1100:2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_1</t>
@@ -185,12 +191,6 @@
     <t xml:space="preserve">M2 current (mA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 3 (A) position, pulse:1100:2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
-  </si>
-  <si>
     <t xml:space="preserve">Holding_register_4</t>
   </si>
   <si>
@@ -272,37 +272,37 @@
     <t xml:space="preserve">Input_register_7</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 1 :</t>
+    <t xml:space="preserve">Temperature 1 (Sample withdrawal point)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_8</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 2 :</t>
+    <t xml:space="preserve">Temperature 2 (Sample at recirculation point)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_9</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 3 :</t>
+    <t xml:space="preserve">Temperature 3 (Water at withdrawal point)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_10</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 4 :</t>
+    <t xml:space="preserve">Temperature 4 (Water temp at recirculation point)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_11</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 5 :</t>
+    <t xml:space="preserve">Temperature 5 : NA</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_12</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 6 :</t>
+    <t xml:space="preserve">Temperature 6 : NA</t>
   </si>
   <si>
     <t xml:space="preserve">K-Type Thermocouple sensors</t>
@@ -712,161 +712,165 @@
         <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="E14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="3" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
       <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
@@ -874,7 +878,7 @@
         <v>57</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>58</v>
@@ -890,7 +894,7 @@
         <v>60</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>61</v>
@@ -900,12 +904,12 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>63</v>
@@ -915,8 +919,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
-      <c r="B19" s="0"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="3" t="s">
         <v>65</v>
       </c>
@@ -981,39 +985,41 @@
         <v>79</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0"/>
-      <c r="B24" s="9"/>
+      <c r="B24" s="0"/>
       <c r="C24" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+      <c r="B25" s="9"/>
       <c r="C25" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1023,7 +1029,7 @@
         <v>63</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1033,7 +1039,7 @@
         <v>67</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -1043,7 +1049,7 @@
         <v>71</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1051,7 +1057,7 @@
         <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1059,7 +1065,7 @@
         <v>81</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,7 +1149,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1182,28 +1188,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>97</v>
@@ -1211,7 +1217,7 @@
     </row>
     <row r="9" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>98</v>
@@ -1238,39 +1244,39 @@
         <v>20</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1278,7 +1284,7 @@
         <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="100">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">Enable M2 brake</t>
   </si>
   <si>
-    <t xml:space="preserve">Get valve positions</t>
+    <t xml:space="preserve">NA</t>
   </si>
   <si>
     <t xml:space="preserve">Get sample weight (1 value, not avg) </t>
@@ -131,9 +131,6 @@
     <t xml:space="preserve">Coil_5</t>
   </si>
   <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Holding_register_0</t>
   </si>
   <si>
@@ -179,7 +176,7 @@
     <t xml:space="preserve">M1 current (mA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 3 (A) position, pulse:1100:2000</t>
+    <t xml:space="preserve">Set valve 3 (Air/Fluid) position, pulse:1100:2000</t>
   </si>
   <si>
     <t xml:space="preserve">Set pump 2 flow rate, range:0:100</t>
@@ -194,7 +191,7 @@
     <t xml:space="preserve">Holding_register_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 4 (B) position, pulse:1000:1900</t>
+    <t xml:space="preserve">Set valve 4 (Sample/Water) position, pulse:1000:1900</t>
   </si>
   <si>
     <t xml:space="preserve">Humidity (RH)</t>
@@ -203,9 +200,6 @@
     <t xml:space="preserve">Holding_register_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Set valve 5 position(sample or water) pulse:1000:1950</t>
-  </si>
-  <si>
     <t xml:space="preserve">Temperature (deg C)</t>
   </si>
   <si>
@@ -272,25 +266,25 @@
     <t xml:space="preserve">Input_register_7</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 1 (Sample withdrawal point)</t>
+    <t xml:space="preserve">Temperature 1 (Room temperature)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_8</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 2 (Sample at recirculation point)</t>
+    <t xml:space="preserve">Temperature 2 (After radiator)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_9</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 3 (Water at withdrawal point)</t>
+    <t xml:space="preserve">Temperature 3 (Before radiator)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_10</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 4 (Water temp at recirculation point)</t>
+    <t xml:space="preserve">Temperature 4 (Recirculation point)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_11</t>
@@ -761,24 +755,24 @@
         <v>35</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>25</v>
@@ -786,118 +780,118 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="5" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="8"/>
       <c r="C17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="AMI17" s="0"/>
       <c r="AMJ17" s="0"/>
@@ -906,74 +900,74 @@
       <c r="A18" s="7"/>
       <c r="B18" s="8"/>
       <c r="C18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0"/>
       <c r="B20" s="0"/>
       <c r="C20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="F20" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0"/>
       <c r="B21" s="0"/>
       <c r="C21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="F21" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0"/>
       <c r="B22" s="0"/>
       <c r="C22" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -982,10 +976,10 @@
       <c r="A23" s="0"/>
       <c r="B23" s="0"/>
       <c r="C23" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -994,10 +988,10 @@
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1006,114 +1000,114 @@
       <c r="A25" s="0"/>
       <c r="B25" s="9"/>
       <c r="C25" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1149,14 +1143,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1172,7 +1166,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1180,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1188,7 +1182,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1196,47 +1190,47 @@
         <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1244,7 +1238,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1252,7 +1246,7 @@
         <v>24</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1260,7 +1254,7 @@
         <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1268,23 +1262,23 @@
         <v>35</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/sample_separation_system_modbus_config.xlsx
+++ b/sample_separation_system_modbus_config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="88">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -197,69 +197,33 @@
     <t xml:space="preserve">Humidity (RH)</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Temperature (deg C)</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Input_register_2</t>
   </si>
   <si>
     <t xml:space="preserve">Weight (grams)</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set water cut off temperature, range:20:50:0.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Input_register_3</t>
   </si>
   <si>
     <t xml:space="preserve">Un-tared weight(grams)</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set sample cut off temperature, range:20:50:0.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Input_register_4</t>
   </si>
   <si>
     <t xml:space="preserve">Motor 1 current sense (mA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set water pump, range:0:100</t>
-  </si>
-  <si>
     <t xml:space="preserve">Input_register_5</t>
   </si>
   <si>
     <t xml:space="preserve">Motor 2 current sense (mA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Holding_register_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set sample pump, range:0:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding_register_12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Input_register_6</t>
   </si>
   <si>
@@ -272,31 +236,31 @@
     <t xml:space="preserve">Input_register_8</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 2 (After radiator)</t>
+    <t xml:space="preserve">Temperature 2 (Sample before radiator)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_9</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 3 (Before radiator)</t>
+    <t xml:space="preserve">Temperature 3 (Water before radiator)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_10</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 4 (Recirculation point)</t>
+    <t xml:space="preserve">Temperature 4 (Fluid after radiator)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_11</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 5 : NA</t>
+    <t xml:space="preserve">Temperature 5 (Recirculation point)</t>
   </si>
   <si>
     <t xml:space="preserve">Input_register_12</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature 6 : NA</t>
+    <t xml:space="preserve">Temperature 6 (Infuse to Flow Cell)</t>
   </si>
   <si>
     <t xml:space="preserve">K-Type Thermocouple sensors</t>
@@ -546,13 +510,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMJ41"/>
+  <dimension ref="A1:AMJ33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="41.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.91"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="11.52"/>
@@ -858,7 +822,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>53</v>
       </c>
@@ -878,11 +842,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="8"/>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>22</v>
@@ -891,7 +855,7 @@
         <v>53</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AMI17" s="0"/>
       <c r="AMJ17" s="0"/>
@@ -900,74 +864,74 @@
       <c r="A18" s="7"/>
       <c r="B18" s="8"/>
       <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0"/>
       <c r="B20" s="0"/>
       <c r="C20" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0"/>
       <c r="B21" s="0"/>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0"/>
       <c r="B22" s="0"/>
       <c r="C22" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -976,7 +940,7 @@
       <c r="A23" s="0"/>
       <c r="B23" s="0"/>
       <c r="C23" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>22</v>
@@ -988,10 +952,10 @@
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1000,131 +964,67 @@
       <c r="A25" s="0"/>
       <c r="B25" s="9"/>
       <c r="C25" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="3" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>22</v>
+        <v>76</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>22</v>
+        <v>78</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="C32" s="0"/>
+      <c r="D32" s="0"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="0"/>
-      <c r="D40" s="0"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="0"/>
-      <c r="D41" s="0"/>
+      <c r="C33" s="0"/>
+      <c r="D33" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1143,14 +1043,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1166,7 +1066,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1174,7 +1074,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1206,7 +1106,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1214,23 +1114,23 @@
         <v>53</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1275,7 +1175,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>22</v>
